--- a/corporates/FC_Urban_London_corporates_batch2_Sep2026.xlsx
+++ b/corporates/FC_Urban_London_corporates_batch2_Sep2026.xlsx
@@ -1364,7 +1364,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Third Floor, 81 Southwark Street</t>
+          <t>81 Southwark Street</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       <c r="T10" s="3" t="inlineStr">
         <is>
           <t>Hi Drew,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 7 minute walk from your office on Third Floor, 81 Southwark Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 7 minute walk from your office at 81 Southwark Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -1512,7 +1512,7 @@
       <c r="T11" s="3" t="inlineStr">
         <is>
           <t>Hi EAM London team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 8 minute walk from your office at 215-221 Borough High Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about an 8 minute walk from your office at 215-221 Borough High Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -1607,7 +1607,7 @@
         <is>
           <t>Hi Cezanne HR team,
 Congratulations on winning the 2026 Talent Tech Customer Service Award, presented in London this September.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 8 minute walk from your office at 57 Southwark Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about an 8 minute walk from your office at 57 Southwark Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -1693,7 +1693,7 @@
       <c r="T13" s="3" t="inlineStr">
         <is>
           <t>Hi PensionBee team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 8 minute walk from your office at 209 Blackfriars Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about an 8 minute walk from your office at 209 Blackfriars Road.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2155,7 +2155,7 @@
         <is>
           <t>Hi ECD Architects team,
 Congratulations on ECD Architects making Building magazine's 2026 Top 150 Consultants list, ranking joint 36th among the Top 50 Architects.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 11 minute walk from your office at 65 Hopton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about an 11 minute walk from your office at 65 Hopton Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2336,7 +2336,7 @@
         <is>
           <t>Hi Winckworth Sherwood team,
 Congratulations on welcoming Sean Houlihan as a new partner in the banking and finance team this September.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 12 minute walk from your office on Arbor, 255 Blackfriars Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 12 minute walk from your office at Arbor, 255 Blackfriars Road.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2611,7 +2611,7 @@
         <is>
           <t>Hi Hanover team,
 Congratulations on Anita Boateng joining as President in June to lead your next phase of growth.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 13 minute walk from your office on Riverside House, 2a Southwark Bridge Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 13 minute walk from your office at Riverside House, 2a Southwark Bridge Road.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2697,7 +2697,7 @@
       <c r="T24" s="3" t="inlineStr">
         <is>
           <t>Hi Madano team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 13 minute walk from your office on Riverside House, 2a Southwark Bridge Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 13 minute walk from your office at Riverside House, 2a Southwark Bridge Road.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2869,7 +2869,7 @@
       <c r="T26" s="3" t="inlineStr">
         <is>
           <t>Hi Kreab team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 15 minute walk from your office on The Shard, 32 London Bridge Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 15 minute walk from your office at The Shard, 32 London Bridge Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -2955,7 +2955,7 @@
       <c r="T27" s="3" t="inlineStr">
         <is>
           <t>Hi MOBKOI team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 15 minute walk from your office on The Shard, 32 London Bridge Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Borough Academy, about a 15 minute walk from your office at The Shard, 32 London Bridge Street.
 We currently have space there on Thursdays at 20:00 and Fridays at 17:30 or 18:30.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -3213,7 +3213,7 @@
       <c r="T30" s="3" t="inlineStr">
         <is>
           <t>Hi Khalij Group team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Poplar pitch on Poplar High Street, about a 7 minute walk from your office on One Canada Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Poplar pitch on Poplar High Street, about a 7 minute walk from your office at One Canada Square.
 We currently have space there on Tuesdays at 20:00 every week and every other Thursday at 20:00.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -3308,7 +3308,7 @@
         <is>
           <t>Hi Datatonic team,
 I saw Datatonic won two Google Cloud Partner of the Year awards this year, including UK and Ireland Country Partner.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Poplar pitch on Poplar High Street, about a 7 minute walk from your office on One Canada Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Poplar pitch on Poplar High Street, about a 7 minute walk from your office at One Canada Square.
 We currently have space there on Tuesdays at 20:00 every week and every other Thursday at 20:00.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
@@ -3485,7 +3485,7 @@
       <c r="T33" s="3" t="inlineStr">
         <is>
           <t>Hi Feilden+Mawson team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 8 minute walk from your office at 21-27 Lamb's Conduit Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 8 minute walk from your office at 21-27 Lamb's Conduit Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -3735,7 +3735,7 @@
       <c r="T36" s="3" t="inlineStr">
         <is>
           <t>Hi Insite Risk Management team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 11 minute walk from your office at 221 Pentonville Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 221 Pentonville Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -3824,7 +3824,7 @@
       <c r="T37" s="3" t="inlineStr">
         <is>
           <t>Hi Jimmy,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 11 minute walk from your office at 25 Easton Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 25 Easton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6230,7 +6230,7 @@
         <is>
           <t>Hi Essentia Analytics team,
 Congratulations on the launch of Stock Market Maestros, the book your CEO Clare Flynn Levy helped write, published this March.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 8 minute walk from your office at 1 Mark Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office at 1 Mark Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6309,7 +6309,7 @@
       <c r="T66" s="3" t="inlineStr">
         <is>
           <t>Hi Flexciton team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 8 minute walk from your office on Curtain Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office on Curtain Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6804,7 +6804,7 @@
       <c r="T72" s="3" t="inlineStr">
         <is>
           <t>Hi Rosco team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Rosemary Gardens in Islington, about a 8 minute walk from your office on De Beauvoir Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Rosemary Gardens in Islington, about an 8 minute walk from your office on De Beauvoir Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7226,7 +7226,7 @@
       <c r="T77" s="3" t="inlineStr">
         <is>
           <t>Hi Gemic team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office on Michelin House, 81 Fulham Road.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office at Michelin House, 81 Fulham Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7577,7 +7577,7 @@
       <c r="T81" s="3" t="inlineStr">
         <is>
           <t>Hi Kefron team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 11 minute walk from your office at 21 Ellis Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 21 Ellis Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7658,7 +7658,7 @@
       <c r="T82" s="3" t="inlineStr">
         <is>
           <t>Hi venturethree team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 11 minute walk from your office at 11 Cavalry Square.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 11 Cavalry Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8679,7 +8679,7 @@
       <c r="T94" s="3" t="inlineStr">
         <is>
           <t>Hi DVF Recruitment team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 8 minute walk from your office at 10-12 Alie Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 8 minute walk from your office at 10-12 Alie Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8939,7 +8939,7 @@
         <is>
           <t>Hi Northell team,
 Congratulations on your December 2025 partnership with Clearcast, bringing Northell's explainable AI to UK television ad clearance.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office on Heron Tower, 110 Bishopsgate.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at Heron Tower, 110 Bishopsgate.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9049,7 +9049,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>18th Floor, 100 Bishopsgate</t>
+          <t>100 Bishopsgate</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       <c r="T99" s="3" t="inlineStr">
         <is>
           <t>Hi Celon team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 18th Floor, 100 Bishopsgate.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 100 Bishopsgate.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9287,7 +9287,7 @@
         <is>
           <t>Hi Two Three Bird team,
 I saw your Sundays brand launched new electric bike insurance cover for UK delivery riders this January.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 11 minute walk from your office at 5 St Helen's Place.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 11 minute walk from your office at 5 St Helen's Place.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,

--- a/corporates/FC_Urban_London_corporates_batch2_Sep2026.xlsx
+++ b/corporates/FC_Urban_London_corporates_batch2_Sep2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Batch 2'!$A$1:$T$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Batch 2'!$A$1:$T$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T104"/>
+  <dimension ref="A1:T107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3667,30 +3667,30 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Insite Risk Management</t>
+          <t>Acaster Lloyd</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://www.insiteriskmanagement.com</t>
+          <t>https://acasterlloyd.com</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>221 Pentonville Road</t>
+          <t>84 Theobalds Road</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>N1 9UZ</t>
+          <t>WC1X 8NL</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>info@insiteriskmanagement.com</t>
+          <t>hello@acasterlloyd.com</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -3714,8 +3714,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on completing your move to full employee ownership as an EOT in February this year.</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thrings.com/blog/acaster-lloyd-eot</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -3729,13 +3737,14 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Insite Risk Management team</t>
+          <t>Weekly football for the Acaster Lloyd team</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>Hi Insite Risk Management team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 221 Pentonville Road.
+          <t>Hi Acaster Lloyd team,
+Congratulations on completing your move to full employee ownership as an EOT in February this year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 9 minute walk from your office at 84 Theobalds Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -3748,30 +3757,30 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Bespoke Careers</t>
+          <t>Medical Architecture</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://www.bespokecareers.com</t>
+          <t>https://www.medicalarchitecture.com</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25 Easton Street</t>
+          <t>4 Northington Street</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>WC1X 0DS</t>
+          <t>WC1N 2JG</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3780,22 +3789,22 @@
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Jimmy Bent</t>
+          <t>Ruairi Reeves</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>jimmy@bespokecareers.com</t>
+          <t>ruairi.reeves@medicalarchitecture.com</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -3803,8 +3812,16 @@
           <t>named</t>
         </is>
       </c>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on celebrating 35 years of Medical Architecture this month, quite a milestone for the practice.</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>https://medicalarchitecture.com/celebrating-35-years-of-medical-architecture/</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -3818,13 +3835,14 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Bespoke Careers team</t>
+          <t>Weekly football for the Medical Architecture team</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>Hi Jimmy,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 25 Easton Street.
+          <t>Hi Ruairi,
+Congratulations on celebrating 35 years of Medical Architecture this month, quite a milestone for the practice.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 9 minute walk from your office at 4 Northington Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -3837,30 +3855,30 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>JasperRose</t>
+          <t>Insite Risk Management</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://jasperrose.co.uk</t>
+          <t>https://www.insiteriskmanagement.com</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20 Red Lion Street</t>
+          <t>221 Pentonville Road</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>WC1R 4PS</t>
+          <t>N1 9UZ</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3869,27 +3887,19 @@
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Rosie O'Callaghan</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Co-Founder &amp; Director</t>
-        </is>
-      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>rosie@jasperrose.co.uk</t>
+          <t>info@insiteriskmanagement.com</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>named</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr"/>
@@ -3907,13 +3917,13 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the JasperRose team</t>
+          <t>Weekly football for the Insite Risk Management team</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>Hi Rosie,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 12 minute walk from your office at 20 Red Lion Street.
+          <t>Hi Insite Risk Management team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 221 Pentonville Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -3926,30 +3936,30 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Easton Bevins</t>
+          <t>Bespoke Careers</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://www.eastonbevins.co.uk</t>
+          <t>https://www.bespokecareers.com</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Other professional services</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>10 Gray's Inn Square</t>
+          <t>25 Easton Street</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>WC1R 5JD</t>
+          <t>WC1X 0DS</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3958,19 +3968,27 @@
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Jimmy Bent</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>info@eastonbevins.co.uk</t>
+          <t>jimmy@bespokecareers.com</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>named</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr"/>
@@ -3988,13 +4006,13 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Easton Bevins team</t>
+          <t>Weekly football for the Bespoke Careers team</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>Hi Easton Bevins team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 13 minute walk from your office at 10 Gray's Inn Square.
+          <t>Hi Jimmy,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about an 11 minute walk from your office at 25 Easton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4007,28 +4025,30 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Meniga</t>
+          <t>JasperRose</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://www.meniga.com</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
+          <t>https://jasperrose.co.uk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19 Bloomsbury Way</t>
+          <t>20 Red Lion Street</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>WC1A 2TH</t>
+          <t>WC1R 4PS</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4037,39 +4057,31 @@
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Marzena Wiecko</t>
+          <t>Rosie O'Callaghan</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>VP of People &amp; Culture</t>
+          <t>Co-Founder &amp; Director</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>info@meniga.com</t>
+          <t>rosie@jasperrose.co.uk</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t>I saw that Meniga appointed Piotr Tybura as its new Chief Technology Officer earlier this year.</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>https://www.meniga.com/resources/meniga-appoints-veteran-technology-leader-as-chief-technology-officer/</t>
-        </is>
-      </c>
+          <t>named</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -4083,14 +4095,13 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Meniga team</t>
+          <t>Weekly football for the JasperRose team</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>Hi Marzena,
-I saw that Meniga appointed Piotr Tybura as its new Chief Technology Officer earlier this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 19 Bloomsbury Way.
+          <t>Hi Rosie,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 12 minute walk from your office at 20 Red Lion Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4103,28 +4114,30 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Freshminds</t>
+          <t>Teacher Stern</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://www.freshminds.co.uk</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>https://www.teacherstern.com</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>138</v>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>229-231 High Holborn</t>
+          <t>37-41 Bedford Row</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>WC1V 7DA</t>
+          <t>WC1R 4JH</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4133,14 +4146,14 @@
         </is>
       </c>
       <c r="H41" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>info@freshminds.co.uk</t>
+          <t>contact@teacherstern.com</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -4163,13 +4176,13 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Freshminds team</t>
+          <t>Weekly football for the Teacher Stern team</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>Hi Freshminds team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 229-231 High Holborn.
+          <t>Hi Teacher Stern team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 12 minute walk from your office at 37-41 Bedford Row.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4182,28 +4195,30 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Tradewind Recruitment</t>
+          <t>Easton Bevins</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://www.twrecruitment.com</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>https://www.eastonbevins.co.uk</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>35</v>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Other professional services</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>110 High Holborn</t>
+          <t>10 Gray's Inn Square</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>WC1V 6JS</t>
+          <t>WC1R 5JD</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -4212,14 +4227,14 @@
         </is>
       </c>
       <c r="H42" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>london@twrecruitment.com</t>
+          <t>info@eastonbevins.co.uk</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -4242,13 +4257,13 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Tradewind Recruitment team</t>
+          <t>Weekly football for the Easton Bevins team</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>Hi Tradewind Recruitment team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 110 High Holborn.
+          <t>Hi Easton Bevins team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 13 minute walk from your office at 10 Gray's Inn Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4261,30 +4276,28 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Aimsun</t>
+          <t>Meniga</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://www.aimsun.com</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="n">
-        <v>101</v>
-      </c>
+          <t>https://www.meniga.com</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>125 Kingsway (Aviation House)</t>
+          <t>19 Bloomsbury Way</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>WC2B 6NH</t>
+          <t>WC1A 2TH</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -4293,14 +4306,22 @@
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Marzena Wiecko</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>VP of People &amp; Culture</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>info@aimsun.com</t>
+          <t>info@meniga.com</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -4310,12 +4331,12 @@
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on winning the 2026 CIHT Technology and Digital Transformation Award for the Tees Valley digital twin in June.</t>
+          <t>I saw that Meniga appointed Piotr Tybura as its new Chief Technology Officer earlier this year.</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>https://www.aimsun.com/newsroom/</t>
+          <t>https://www.meniga.com/resources/meniga-appoints-veteran-technology-leader-as-chief-technology-officer/</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -4331,14 +4352,14 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Aimsun team</t>
+          <t>Weekly football for the Meniga team</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>Hi Aimsun team,
-Congratulations on winning the 2026 CIHT Technology and Digital Transformation Award for the Tees Valley digital twin in June.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 125 Kingsway (Aviation House).
+          <t>Hi Marzena,
+I saw that Meniga appointed Piotr Tybura as its new Chief Technology Officer earlier this year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 19 Bloomsbury Way.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4351,30 +4372,28 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MishiPay</t>
+          <t>Freshminds</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://mishipay.com</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n">
-        <v>73</v>
-      </c>
+          <t>https://www.freshminds.co.uk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>125 Kingsway (Aviation House)</t>
+          <t>229-231 High Holborn</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>WC2B 6NH</t>
+          <t>WC1V 7DA</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -4383,14 +4402,14 @@
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>info@mishipay.com</t>
+          <t>info@freshminds.co.uk</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -4413,13 +4432,13 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the MishiPay team</t>
+          <t>Weekly football for the Freshminds team</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>Hi MishiPay team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 125 Kingsway (Aviation House).
+          <t>Hi Freshminds team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 229-231 High Holborn.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4432,30 +4451,28 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Buildots</t>
+          <t>Tradewind Recruitment</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://buildots.com</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="n">
-        <v>350</v>
-      </c>
+          <t>https://www.twrecruitment.com</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>262 High Holborn</t>
+          <t>110 High Holborn</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>WC1V 7EE</t>
+          <t>WC1V 6JS</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -4464,14 +4481,14 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>info@buildots.com</t>
+          <t>london@twrecruitment.com</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -4479,16 +4496,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on acquiring Genda in October to bring workforce insights into your construction platform.</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>https://buildots.com/blog/buildots-acquires-genda/</t>
-        </is>
-      </c>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -4502,14 +4511,13 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Buildots team</t>
+          <t>Weekly football for the Tradewind Recruitment team</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>Hi Buildots team,
-Congratulations on acquiring Genda in October to bring workforce insights into your construction platform.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 262 High Holborn.
+          <t>Hi Tradewind Recruitment team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 14 minute walk from your office at 110 High Holborn.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4522,30 +4530,30 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Satago</t>
+          <t>Aimsun</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://www.satago.com</t>
+          <t>https://www.aimsun.com</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>88 Kingsway</t>
+          <t>125 Kingsway (Aviation House)</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>WC2B 6AA</t>
+          <t>WC2B 6NH</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -4561,7 +4569,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>hello@satago.com</t>
+          <t>info@aimsun.com</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -4571,12 +4579,12 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on Satago's expanded partnership with Sage this July to help small businesses manage cash flow.</t>
+          <t>Congratulations on winning the 2026 CIHT Technology and Digital Transformation Award for the Tees Valley digital twin in June.</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>https://www.sage.com/investors/investor-downloads/press-releases/2026/07/sage-and-satago-expand-partnership/</t>
+          <t>https://www.aimsun.com/newsroom/</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -4592,14 +4600,14 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Satago team</t>
+          <t>Weekly football for the Aimsun team</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>Hi Satago team,
-Congratulations on Satago's expanded partnership with Sage this July to help small businesses manage cash flow.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 88 Kingsway.
+          <t>Hi Aimsun team,
+Congratulations on winning the 2026 CIHT Technology and Digital Transformation Award for the Tees Valley digital twin in June.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 125 Kingsway (Aviation House).
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4612,30 +4620,30 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Joseph Hage Aaronson &amp; Bremen</t>
+          <t>MishiPay</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://uk.jha.com</t>
+          <t>https://mishipay.com</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>280 High Holborn</t>
+          <t>125 Kingsway (Aviation House)</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>WC1V 7EE</t>
+          <t>WC2B 6NH</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4651,7 +4659,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>info@jha.com</t>
+          <t>info@mishipay.com</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -4674,13 +4682,13 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Joseph Hage Aaronson &amp; Bremen team</t>
+          <t>Weekly football for the MishiPay team</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>Hi Joseph Hage Aaronson &amp; Bremen team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 280 High Holborn.
+          <t>Hi MishiPay team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 125 Kingsway (Aviation House).
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4693,30 +4701,30 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Park Avenue Recruitment</t>
+          <t>Buildots</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://www.park-avenue.co.uk</t>
+          <t>https://buildots.com</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>27</v>
+        <v>350</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>37-39 High Holborn</t>
+          <t>262 High Holborn</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>WC1V 6AA</t>
+          <t>WC1V 7EE</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4732,7 +4740,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>info@park-avenue.co.uk</t>
+          <t>info@buildots.com</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -4740,8 +4748,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N48" s="3" t="inlineStr"/>
-      <c r="O48" s="2" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on acquiring Genda in October to bring workforce insights into your construction platform.</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>https://buildots.com/blog/buildots-acquires-genda/</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -4755,13 +4771,14 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Park Avenue Recruitment team</t>
+          <t>Weekly football for the Buildots team</t>
         </is>
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>Hi Park Avenue Recruitment team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 37-39 High Holborn.
+          <t>Hi Buildots team,
+Congratulations on acquiring Genda in October to bring workforce insights into your construction platform.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 262 High Holborn.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4774,46 +4791,46 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Webb Yates</t>
+          <t>Satago</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://www.webbyates.com</t>
+          <t>https://www.satago.com</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Engineering consultancy</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>14 Wharf Road</t>
+          <t>88 Kingsway</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>N1 7RW</t>
+          <t>WC2B 6AA</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Moreland School on Gard Street</t>
+          <t>Coram's Fields</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>london@webbyates.com</t>
+          <t>hello@satago.com</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -4823,12 +4840,12 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on TBC London winning a BCO regional ESG Award this year for large scale structural steel reuse.</t>
+          <t>Congratulations on Satago's expanded partnership with Sage this July to help small businesses manage cash flow.</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>https://webbyates.com/news/tbc-london-receives-bco-regional-esg-award/</t>
+          <t>https://www.sage.com/investors/investor-downloads/press-releases/2026/07/sage-and-satago-expand-partnership/</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -4839,19 +4856,19 @@
       <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
+          <t>https://www.fcurban.com/location/st-pancras-corams-fields-3g</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Webb Yates team</t>
+          <t>Weekly football for the Satago team</t>
         </is>
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>Hi Webb Yates team,
-Congratulations on TBC London winning a BCO regional ESG Award this year for large scale structural steel reuse.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 4 minute walk from your office at 14 Wharf Road.
+          <t>Hi Satago team,
+Congratulations on Satago's expanded partnership with Sage this July to help small businesses manage cash flow.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 88 Kingsway.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4864,44 +4881,46 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MJCP</t>
+          <t>Joseph Hage Aaronson &amp; Bremen</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://www.mjcp.co.uk</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
+          <t>https://uk.jha.com</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>47</v>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>230 City Road</t>
+          <t>280 High Holborn</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>EC1V 2TT</t>
+          <t>WC1V 7EE</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Moreland School on Gard Street</t>
+          <t>Coram's Fields</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>talk@mjcp.co.uk</t>
+          <t>info@jha.com</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -4919,18 +4938,18 @@
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
+          <t>https://www.fcurban.com/location/st-pancras-corams-fields-3g</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the MJCP team</t>
+          <t>Weekly football for the Joseph Hage Aaronson &amp; Bremen team</t>
         </is>
       </c>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>Hi MJCP team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 5 minute walk from your office at 230 City Road.
+          <t>Hi Joseph Hage Aaronson &amp; Bremen team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 280 High Holborn.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -4943,46 +4962,46 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Made by Many</t>
+          <t>Park Avenue Recruitment</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://www.madebymany.com</t>
+          <t>https://www.park-avenue.co.uk</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>38 Graham Street</t>
+          <t>37-39 High Holborn</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>N1 8JX</t>
+          <t>WC1V 6AA</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>Moreland School on Gard Street</t>
+          <t>Coram's Fields</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>contact@madebymany.com</t>
+          <t>info@park-avenue.co.uk</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -5000,18 +5019,18 @@
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
+          <t>https://www.fcurban.com/location/st-pancras-corams-fields-3g</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Made by Many team</t>
+          <t>Weekly football for the Park Avenue Recruitment team</t>
         </is>
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>Hi Made by Many team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 6 minute walk from your office at 38 Graham Street.
+          <t>Hi Park Avenue Recruitment team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Coram's Fields, about a 15 minute walk from your office at 37-39 High Holborn.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5024,16 +5043,16 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Curtins</t>
+          <t>Webb Yates</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://www.curtins.com</t>
+          <t>https://www.webbyates.com</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
@@ -5042,12 +5061,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>40 Compton Street</t>
+          <t>14 Wharf Road</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>EC1V 0BD</t>
+          <t>N1 7RW</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -5056,14 +5075,14 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>info@curtins.com</t>
+          <t>london@webbyates.com</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -5073,12 +5092,12 @@
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on being named AUDE Supplier of the Year in May this year.</t>
+          <t>Congratulations on TBC London winning a BCO regional ESG Award this year for large scale structural steel reuse.</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>https://www.curtins.com/news/</t>
+          <t>https://webbyates.com/news/tbc-london-receives-bco-regional-esg-award/</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -5094,14 +5113,14 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Curtins team</t>
+          <t>Weekly football for the Webb Yates team</t>
         </is>
       </c>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>Hi Curtins team,
-Congratulations on being named AUDE Supplier of the Year in May this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 7 minute walk from your office at 40 Compton Street.
+          <t>Hi Webb Yates team,
+Congratulations on TBC London winning a BCO regional ESG Award this year for large scale structural steel reuse.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 4 minute walk from your office at 14 Wharf Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5114,30 +5133,28 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Broadgate</t>
+          <t>MJCP</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://www.broadgatesearch.com</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>60</v>
-      </c>
+          <t>https://www.mjcp.co.uk</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>20 Westland Place</t>
+          <t>230 City Road</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>N1 7JR</t>
+          <t>EC1V 2TT</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -5146,14 +5163,14 @@
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>enquiries@broadgatesearch.com</t>
+          <t>talk@mjcp.co.uk</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -5176,13 +5193,13 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Broadgate team</t>
+          <t>Weekly football for the MJCP team</t>
         </is>
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>Hi Broadgate team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 9 minute walk from your office at 20 Westland Place.
+          <t>Hi MJCP team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 5 minute walk from your office at 230 City Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5195,30 +5212,30 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Hawkins\Brown</t>
+          <t>Made by Many</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://www.hawkinsbrown.com</t>
+          <t>https://www.madebymany.com</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>30 Clerkenwell Road</t>
+          <t>38 Graham Street</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>EC1M 5PG</t>
+          <t>N1 8JX</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -5227,14 +5244,14 @@
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>mail@hawkinsbrown.com</t>
+          <t>contact@madebymany.com</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -5242,16 +5259,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N54" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on being appointed by City Hall last October to help lead the regeneration of Oxford Street.</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hawkinsbrown.com/news/</t>
-        </is>
-      </c>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -5265,14 +5274,13 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Hawkins\Brown team</t>
+          <t>Weekly football for the Made by Many team</t>
         </is>
       </c>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>Hi Hawkins\Brown team,
-Congratulations on being appointed by City Hall last October to help lead the regeneration of Oxford Street.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 10 minute walk from your office at 30 Clerkenwell Road.
+          <t>Hi Made by Many team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 6 minute walk from your office at 38 Graham Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5285,28 +5293,30 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>BriteSpark Films</t>
+          <t>Curtins</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://britesparkfilms.com</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr"/>
+          <t>https://www.curtins.com</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Other professional services</t>
+          <t>Engineering consultancy</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>St Peter's Street</t>
+          <t>40 Compton Street</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>N1 8JD</t>
+          <t>EC1V 0BD</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -5315,22 +5325,14 @@
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>We pride</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>People</t>
-        </is>
-      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>info@britesparkfilms.com</t>
+          <t>info@curtins.com</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -5340,12 +5342,12 @@
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on your Dispatches documentary being nominated for Best Documentary at the RTS East Programme Awards in May 2026.</t>
+          <t>Congratulations on being named AUDE Supplier of the Year in May this year.</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>https://britesparkfilms.com/news/</t>
+          <t>https://www.curtins.com/news/</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -5361,14 +5363,14 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the BriteSpark Films team</t>
+          <t>Weekly football for the Curtins team</t>
         </is>
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>Hi Tom,
-Congratulations on your Dispatches documentary being nominated for Best Documentary at the RTS East Programme Awards in May 2026.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office on St Peter's Street.
+          <t>Hi Curtins team,
+Congratulations on being named AUDE Supplier of the Year in May this year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 7 minute walk from your office at 40 Compton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5381,30 +5383,30 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Thriva</t>
+          <t>Broadgate</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://thriva.co:443</t>
+          <t>https://www.broadgatesearch.com</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Old Street Yard</t>
+          <t>20 Westland Place</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>EC1Y 8AF</t>
+          <t>N1 7JR</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -5413,14 +5415,14 @@
         </is>
       </c>
       <c r="H56" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>hello@thriva.co</t>
+          <t>enquiries@broadgatesearch.com</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
@@ -5443,13 +5445,13 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Thriva team</t>
+          <t>Weekly football for the Broadgate team</t>
         </is>
       </c>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>Hi Thriva team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office on Old Street Yard.
+          <t>Hi Broadgate team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 9 minute walk from your office at 20 Westland Place.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5462,30 +5464,30 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Capital Law</t>
+          <t>Hawkins\Brown</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://www.capitallaw.co.uk</t>
+          <t>https://www.hawkinsbrown.com</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>104D St John Street</t>
+          <t>30 Clerkenwell Road</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>EC1M 4EH</t>
+          <t>EC1M 5PG</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -5494,14 +5496,14 @@
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>info@capitallaw.co.uk</t>
+          <t>mail@hawkinsbrown.com</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -5511,12 +5513,12 @@
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on being shortlisted for the 2026 Innovative Lawyers Awards Europe this month.</t>
+          <t>Congratulations on being appointed by City Hall last October to help lead the regeneration of Oxford Street.</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>https://www.capitallaw.co.uk/</t>
+          <t>https://www.hawkinsbrown.com/news/</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -5532,14 +5534,14 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Capital Law team</t>
+          <t>Weekly football for the Hawkins\Brown team</t>
         </is>
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>Hi Capital Law team,
-Congratulations on being shortlisted for the 2026 Innovative Lawyers Awards Europe this month.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office at 104D St John Street.
+          <t>Hi Hawkins\Brown team,
+Congratulations on being appointed by City Hall last October to help lead the regeneration of Oxford Street.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 10 minute walk from your office at 30 Clerkenwell Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5552,30 +5554,28 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Validis</t>
+          <t>BriteSpark Films</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://www.validis.com</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>67</v>
-      </c>
+          <t>https://britesparkfilms.com</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Other professional services</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>16 St John's Lane</t>
+          <t>St Peter's Street</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>EC1M 4BS</t>
+          <t>N1 8JD</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -5584,14 +5584,22 @@
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>We pride</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>info@validis.com</t>
+          <t>info@britesparkfilms.com</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -5599,8 +5607,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N58" s="3" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr"/>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on your Dispatches documentary being nominated for Best Documentary at the RTS East Programme Awards in May 2026.</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>https://britesparkfilms.com/news/</t>
+        </is>
+      </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -5614,13 +5630,14 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Validis team</t>
+          <t>Weekly football for the BriteSpark Films team</t>
         </is>
       </c>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>Hi Validis team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 14 minute walk from your office at 16 St John's Lane.
+          <t>Hi Tom,
+Congratulations on your Dispatches documentary being nominated for Best Documentary at the RTS East Programme Awards in May 2026.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office on St Peter's Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5633,30 +5650,30 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>FIECON</t>
+          <t>Thriva</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://www.fiecon.com</t>
+          <t>https://thriva.co:443</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>30 Farringdon Lane (Hodgkin Huxley House)</t>
+          <t>Old Street Yard</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>EC1R 3AW</t>
+          <t>EC1Y 8AF</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5665,14 +5682,14 @@
         </is>
       </c>
       <c r="H59" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>hello@fiecon.com</t>
+          <t>hello@thriva.co</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -5680,16 +5697,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N59" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on Acumetis launching in April as your newly combined pharma and biotech commercialisation brand.</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>https://www.fiecon.com/</t>
-        </is>
-      </c>
+      <c r="N59" s="3" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -5703,14 +5712,13 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the FIECON team</t>
+          <t>Weekly football for the Thriva team</t>
         </is>
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>Hi FIECON team,
-Congratulations on Acumetis launching in April as your newly combined pharma and biotech commercialisation brand.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 14 minute walk from your office at 30 Farringdon Lane (Hodgkin Huxley House).
+          <t>Hi Thriva team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office on Old Street Yard.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5723,30 +5731,30 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Chetwoods</t>
+          <t>Capital Law</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://www.chetwoods.com</t>
+          <t>https://www.capitallaw.co.uk</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Law</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>13-16 Britton Street</t>
+          <t>104D St John Street</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>EC1M 5SX</t>
+          <t>EC1M 4EH</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -5755,14 +5763,14 @@
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>contact@chetwoods.com</t>
+          <t>info@capitallaw.co.uk</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
@@ -5772,12 +5780,12 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on winning the AJ100 Climate Initiative of the Year award in June for your steel reuse project.</t>
+          <t>Congratulations on being shortlisted for the 2026 Innovative Lawyers Awards Europe this month.</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>https://www.chetwoods.com/insights/chetwoods-wins-aj100-climate-initiative-of-the-year-2026</t>
+          <t>https://www.capitallaw.co.uk/</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -5793,14 +5801,14 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Chetwoods team</t>
+          <t>Weekly football for the Capital Law team</t>
         </is>
       </c>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>Hi Chetwoods team,
-Congratulations on winning the AJ100 Climate Initiative of the Year award in June for your steel reuse project.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 15 minute walk from your office at 13-16 Britton Street.
+          <t>Hi Capital Law team,
+Congratulations on being shortlisted for the 2026 Innovative Lawyers Awards Europe this month.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 13 minute walk from your office at 104D St John Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5813,46 +5821,46 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>St Luke's</t>
+          <t>Validis</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://www.stlukes.co.uk</t>
+          <t>https://www.validis.com</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>12 Fleur De Lis Street</t>
+          <t>16 St John's Lane</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>E1 6BP</t>
+          <t>EC1M 4BS</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Powerleague Shoreditch</t>
+          <t>Moreland School on Gard Street</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>reception@stlukes.co.uk</t>
+          <t>info@validis.com</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
@@ -5860,16 +5868,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N61" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on winning the Bisto account after a competitive pitch back in May, a great win for the team.</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>https://www.moreaboutadvertising.com/2026/05/st-lukes-wins-bisto-creative-after-competitive-pitch/</t>
-        </is>
-      </c>
+      <c r="N61" s="3" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -5878,19 +5878,18 @@
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
+          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the St Luke's team</t>
+          <t>Weekly football for the Validis team</t>
         </is>
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>Hi St Luke's team,
-Congratulations on winning the Bisto account after a competitive pitch back in May, a great win for the team.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 3 minute walk from your office at 12 Fleur De Lis Street.
+          <t>Hi Validis team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 14 minute walk from your office at 16 St John's Lane.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5903,46 +5902,46 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Day Cooper Day</t>
+          <t>FIECON</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://daycooperday.com</t>
+          <t>https://www.fiecon.com</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>53-55 Scrutton Street</t>
+          <t>30 Farringdon Lane (Hodgkin Huxley House)</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>EC2A 4PJ</t>
+          <t>EC1R 3AW</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Powerleague Shoreditch</t>
+          <t>Moreland School on Gard Street</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>hello@daycooperday.com</t>
+          <t>hello@fiecon.com</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -5950,8 +5949,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N62" s="3" t="inlineStr"/>
-      <c r="O62" s="2" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on Acumetis launching in April as your newly combined pharma and biotech commercialisation brand.</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fiecon.com/</t>
+        </is>
+      </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -5960,18 +5967,19 @@
       <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
+          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Day Cooper Day team</t>
+          <t>Weekly football for the FIECON team</t>
         </is>
       </c>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>Hi Day Cooper Day team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 6 minute walk from your office at 53-55 Scrutton Street.
+          <t>Hi FIECON team,
+Congratulations on Acumetis launching in April as your newly combined pharma and biotech commercialisation brand.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 14 minute walk from your office at 30 Farringdon Lane (Hodgkin Huxley House).
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -5984,46 +5992,46 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Words+Pixels</t>
+          <t>Chetwoods</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://www.wordsandpixels.co</t>
+          <t>https://www.chetwoods.com</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>6-8 Standard Place</t>
+          <t>13-16 Britton Street</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>EC2A 3BE</t>
+          <t>EC1M 5SX</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Powerleague Shoreditch</t>
+          <t>Moreland School on Gard Street</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>hello@wordsandpixels.co</t>
+          <t>contact@chetwoods.com</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
@@ -6033,12 +6041,12 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on Words+Pixels winning PRCA Dare's Medium Consultancy of the Year for the second year running.</t>
+          <t>Congratulations on winning the AJ100 Climate Initiative of the Year award in June for your steel reuse project.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://www.wordsandpixels.co/news</t>
+          <t>https://www.chetwoods.com/insights/chetwoods-wins-aj100-climate-initiative-of-the-year-2026</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -6049,19 +6057,19 @@
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
+          <t>https://www.fcurban.com/location/old-st-moreland-primary-school</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Words+Pixels team</t>
+          <t>Weekly football for the Chetwoods team</t>
         </is>
       </c>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>Hi Words+Pixels team,
-Congratulations on Words+Pixels winning PRCA Dare's Medium Consultancy of the Year for the second year running.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 7 minute walk from your office at 6-8 Standard Place.
+          <t>Hi Chetwoods team,
+Congratulations on winning the AJ100 Climate Initiative of the Year award in June for your steel reuse project.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Moreland School on Gard Street, about a 15 minute walk from your office at 13-16 Britton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6074,30 +6082,30 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11:FS</t>
+          <t>St Luke's</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://www.11fs.com</t>
+          <t>https://www.stlukes.co.uk</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>9 Appold Street</t>
+          <t>12 Fleur De Lis Street</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>EC2A 2AP</t>
+          <t>E1 6BP</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -6106,14 +6114,14 @@
         </is>
       </c>
       <c r="H64" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>hello@11fs.com</t>
+          <t>reception@stlukes.co.uk</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
@@ -6121,8 +6129,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N64" s="3" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr"/>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on winning the Bisto account after a competitive pitch back in May, a great win for the team.</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.moreaboutadvertising.com/2026/05/st-lukes-wins-bisto-creative-after-competitive-pitch/</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -6136,13 +6152,14 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the 11:FS team</t>
+          <t>Weekly football for the St Luke's team</t>
         </is>
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>Hi 11:FS team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 7 minute walk from your office at 9 Appold Street.
+          <t>Hi St Luke's team,
+Congratulations on winning the Bisto account after a competitive pitch back in May, a great win for the team.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 3 minute walk from your office at 12 Fleur De Lis Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6155,28 +6172,30 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Essentia Analytics</t>
+          <t>Day Cooper Day</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://www.essentia-analytics.com</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr"/>
+          <t>https://daycooperday.com</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>32</v>
+      </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1 Mark Square</t>
+          <t>53-55 Scrutton Street</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>EC2A 4EG</t>
+          <t>EC2A 4PJ</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -6185,14 +6204,14 @@
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>info@essentia-analytics.com</t>
+          <t>hello@daycooperday.com</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -6200,16 +6219,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N65" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on the launch of Stock Market Maestros, the book your CEO Clare Flynn Levy helped write, published this March.</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>https://www.essentia-analytics.com/</t>
-        </is>
-      </c>
+      <c r="N65" s="3" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -6223,14 +6234,13 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Essentia Analytics team</t>
+          <t>Weekly football for the Day Cooper Day team</t>
         </is>
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>Hi Essentia Analytics team,
-Congratulations on the launch of Stock Market Maestros, the book your CEO Clare Flynn Levy helped write, published this March.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office at 1 Mark Square.
+          <t>Hi Day Cooper Day team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 6 minute walk from your office at 53-55 Scrutton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6243,28 +6253,30 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Flexciton</t>
+          <t>Words+Pixels</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://flexciton.com</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr"/>
+          <t>https://www.wordsandpixels.co</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>30</v>
+      </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Curtain Road</t>
+          <t>6-8 Standard Place</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>EC2A 3BX</t>
+          <t>EC2A 3BE</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -6273,14 +6285,14 @@
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>info@flexciton.com</t>
+          <t>hello@wordsandpixels.co</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
@@ -6288,8 +6300,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N66" s="3" t="inlineStr"/>
-      <c r="O66" s="2" t="inlineStr"/>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on Words+Pixels winning PRCA Dare's Medium Consultancy of the Year for the second year running.</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wordsandpixels.co/news</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -6303,13 +6323,14 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Flexciton team</t>
+          <t>Weekly football for the Words+Pixels team</t>
         </is>
       </c>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>Hi Flexciton team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office on Curtain Road.
+          <t>Hi Words+Pixels team,
+Congratulations on Words+Pixels winning PRCA Dare's Medium Consultancy of the Year for the second year running.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 7 minute walk from your office at 6-8 Standard Place.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6322,28 +6343,30 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Seen Presents</t>
+          <t>11:FS</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://www.seenpresents.com</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr"/>
+          <t>https://www.11fs.com</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>150</v>
+      </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>25 Scrutton Street</t>
+          <t>9 Appold Street</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>EC2A 4HJ</t>
+          <t>EC2A 2AP</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -6352,14 +6375,14 @@
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>info@seenpresents.com</t>
+          <t>hello@11fs.com</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
@@ -6382,13 +6405,13 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Seen Presents team</t>
+          <t>Weekly football for the 11:FS team</t>
         </is>
       </c>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>Hi Seen Presents team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 9 minute walk from your office at 25 Scrutton Street.
+          <t>Hi 11:FS team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 7 minute walk from your office at 9 Appold Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6401,30 +6424,28 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Waugh Thistleton Architects</t>
+          <t>Essentia Analytics</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://waughthistleton.com</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>30</v>
-      </c>
+          <t>https://www.essentia-analytics.com</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>35 Pitfield Street</t>
+          <t>1 Mark Square</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>N1 6HB</t>
+          <t>EC2A 4EG</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -6433,14 +6454,14 @@
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>info@waughthistleton.com</t>
+          <t>info@essentia-analytics.com</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
@@ -6450,12 +6471,12 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on the Travelling Pavilion winning the 2026 CESUGA Innovation Award for showcasing timber in construction.</t>
+          <t>Congratulations on the launch of Stock Market Maestros, the book your CEO Clare Flynn Levy helped write, published this March.</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>https://waughthistleton.com/news/26/07/20/travelling-pavilion-2026-cesuga-innovation-award/</t>
+          <t>https://www.essentia-analytics.com/</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -6471,14 +6492,14 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Waugh Thistleton Architects team</t>
+          <t>Weekly football for the Essentia Analytics team</t>
         </is>
       </c>
       <c r="T68" s="3" t="inlineStr">
         <is>
-          <t>Hi Waugh Thistleton Architects team,
-Congratulations on the Travelling Pavilion winning the 2026 CESUGA Innovation Award for showcasing timber in construction.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office at 35 Pitfield Street.
+          <t>Hi Essentia Analytics team,
+Congratulations on the launch of Stock Market Maestros, the book your CEO Clare Flynn Levy helped write, published this March.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office at 1 Mark Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6491,26 +6512,28 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Action Sustainability</t>
+          <t>Flexciton</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://www.actionsustainability.com</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>20</v>
-      </c>
+          <t>https://flexciton.com</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Curtain Road</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>EC1V 9DD</t>
+          <t>EC2A 3BX</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -6519,22 +6542,14 @@
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>Ian Heptonstall</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Co-Founder &amp; Director</t>
-        </is>
-      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>info@actionsustainability.com</t>
+          <t>info@flexciton.com</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -6557,13 +6572,13 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Action Sustainability team</t>
+          <t>Weekly football for the Flexciton team</t>
         </is>
       </c>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>Hi Ian,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office near EC1V 9DD.
+          <t>Hi Flexciton team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about an 8 minute walk from your office on Curtain Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6576,30 +6591,28 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Pierce Washington</t>
+          <t>Seen Presents</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://piercewashington.com</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>65</v>
-      </c>
+          <t>https://www.seenpresents.com</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Gorsuch Place</t>
+          <t>25 Scrutton Street</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>E2 8JF</t>
+          <t>EC2A 4HJ</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -6608,14 +6621,14 @@
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>info@piercewashington.com</t>
+          <t>info@seenpresents.com</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
@@ -6638,13 +6651,13 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Pierce Washington team</t>
+          <t>Weekly football for the Seen Presents team</t>
         </is>
       </c>
       <c r="T70" s="3" t="inlineStr">
         <is>
-          <t>Hi Pierce Washington team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office on Gorsuch Place.
+          <t>Hi Seen Presents team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 9 minute walk from your office at 25 Scrutton Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6657,30 +6670,30 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Eames Partnership</t>
+          <t>Waugh Thistleton Architects</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://www.eamespartnership.com</t>
+          <t>https://waughthistleton.com</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>1 Finsbury Avenue</t>
+          <t>35 Pitfield Street</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>EC2M 2PF</t>
+          <t>N1 6HB</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -6689,14 +6702,14 @@
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>contact@eamespartnership.com</t>
+          <t>info@waughthistleton.com</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
@@ -6704,8 +6717,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="2" t="inlineStr"/>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on the Travelling Pavilion winning the 2026 CESUGA Innovation Award for showcasing timber in construction.</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>https://waughthistleton.com/news/26/07/20/travelling-pavilion-2026-cesuga-innovation-award/</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -6719,13 +6740,14 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Eames Partnership team</t>
+          <t>Weekly football for the Waugh Thistleton Architects team</t>
         </is>
       </c>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>Hi Eames Partnership team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 13 minute walk from your office at 1 Finsbury Avenue.
+          <t>Hi Waugh Thistleton Architects team,
+Congratulations on the Travelling Pavilion winning the 2026 CESUGA Innovation Award for showcasing timber in construction.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office at 35 Pitfield Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6738,44 +6760,50 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Rosco</t>
+          <t>Action Sustainability</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://www.roscoproduction.com</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
+          <t>https://www.actionsustainability.com</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>De Beauvoir Road</t>
-        </is>
-      </c>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>N1 4EN</t>
+          <t>EC1V 9DD</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Rosemary Gardens in Islington</t>
+          <t>Powerleague Shoreditch</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Ian Heptonstall</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Director</t>
+        </is>
+      </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>london@roscoproduction.com</t>
+          <t>info@actionsustainability.com</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6793,18 +6821,18 @@
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/rosemary-gardens-3g-islington</t>
+          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Rosco team</t>
+          <t>Weekly football for the Action Sustainability team</t>
         </is>
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
-          <t>Hi Rosco team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at Rosemary Gardens in Islington, about an 8 minute walk from your office on De Beauvoir Road.
+          <t>Hi Ian,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office near EC1V 9DD.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6817,59 +6845,51 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Russell Simpson</t>
+          <t>Pierce Washington</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://www.russellsimpson.co.uk</t>
+          <t>https://piercewashington.com</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Other professional services</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>151A Sydney Street</t>
+          <t>Gorsuch Place</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>SW3 6NT</t>
+          <t>E2 8JF</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>our Chelsea pitch on Sydney Street</t>
+          <t>Powerleague Shoreditch</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Hattie Russell</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Head of Operations and People</t>
-        </is>
-      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>hattierussell@russellsimpson.co.uk</t>
+          <t>info@piercewashington.com</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>named</t>
+          <t>generic</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr"/>
@@ -6882,18 +6902,18 @@
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/chelsea</t>
+          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Russell Simpson team</t>
+          <t>Weekly football for the Pierce Washington team</t>
         </is>
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
-          <t>Hi Hattie,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Chelsea pitch on Sydney Street, about a 4 minute walk from your office at 151A Sydney Street.
+          <t>Hi Pierce Washington team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 12 minute walk from your office on Gorsuch Place.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6906,46 +6926,46 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Morris+Company</t>
+          <t>Eames Partnership</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://www.morrisand.company</t>
+          <t>https://www.eamespartnership.com</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>215 Mare Street</t>
+          <t>1 Finsbury Avenue</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>E8 3QE</t>
+          <t>EC2M 2PF</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>our Hackney pitch on Homerton High Street</t>
+          <t>Powerleague Shoreditch</t>
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>london@morrisand.company</t>
+          <t>contact@eamespartnership.com</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
@@ -6953,16 +6973,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N74" s="3" t="inlineStr">
-        <is>
-          <t>In December 2025 the practice won unanimous planning consent for its retrofit of 120 Holborn near Holborn Circus.</t>
-        </is>
-      </c>
-      <c r="O74" s="2" t="inlineStr">
-        <is>
-          <t>https://www.morrisand.company/about</t>
-        </is>
-      </c>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
       <c r="P74" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -6971,19 +6983,18 @@
       <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/hackney</t>
+          <t>https://www.fcurban.com/location/shoreditch-powerleague</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Morris+Company team</t>
+          <t>Weekly football for the Eames Partnership team</t>
         </is>
       </c>
       <c r="T74" s="3" t="inlineStr">
         <is>
-          <t>Hi Morris+Company team,
-In December 2025 the practice won unanimous planning consent for its retrofit of 120 Holborn near Holborn Circus.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Hackney pitch on Homerton High Street, about a 15 minute walk from your office at 215 Mare Street.
+          <t>Hi Eames Partnership team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Powerleague Shoreditch, about a 13 minute walk from your office at 1 Finsbury Avenue.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -6996,46 +7007,44 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Dark Matter Labs</t>
+          <t>Rosco</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://darkmatterlabs.org</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>85</v>
-      </c>
+          <t>https://www.roscoproduction.com</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>217 Mare Street</t>
+          <t>De Beauvoir Road</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>E8 3QE</t>
+          <t>N1 4EN</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>our Hackney pitch on Homerton High Street</t>
+          <t>Rosemary Gardens in Islington</t>
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I75" s="2" t="inlineStr"/>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>info@darkmatterlabs.org</t>
+          <t>london@roscoproduction.com</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
@@ -7053,18 +7062,18 @@
       <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/hackney</t>
+          <t>https://www.fcurban.com/location/rosemary-gardens-3g-islington</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Dark Matter Labs team</t>
+          <t>Weekly football for the Rosco team</t>
         </is>
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>Hi Dark Matter Labs team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Hackney pitch on Homerton High Street, about a 15 minute walk from your office at 217 Mare Street.
+          <t>Hi Rosco team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at Rosemary Gardens in Islington, about an 8 minute walk from your office on De Beauvoir Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7077,51 +7086,59 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LDN Apprenticeships</t>
+          <t>Russell Simpson</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://www.ldnapprenticeships.com</t>
+          <t>https://www.russellsimpson.co.uk</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Other professional services</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>South Lambeth Road</t>
+          <t>151A Sydney Street</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>SW8 1UJ</t>
+          <t>SW3 6NT</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>our Kennington pitch on Hackford Road</t>
+          <t>our Chelsea pitch on Sydney Street</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Hattie Russell</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Head of Operations and People</t>
+        </is>
+      </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>hello@ldnapprenticeships.com</t>
+          <t>hattierussell@russellsimpson.co.uk</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>generic</t>
+          <t>named</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr"/>
@@ -7134,18 +7151,18 @@
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/kennington</t>
+          <t>https://www.fcurban.com/location/chelsea</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the LDN Apprenticeships team</t>
+          <t>Weekly football for the Russell Simpson team</t>
         </is>
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
-          <t>Hi LDN Apprenticeships team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Kennington pitch on Hackford Road, about a 10 minute walk from your office on South Lambeth Road.
+          <t>Hi Hattie,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Chelsea pitch on Sydney Street, about a 4 minute walk from your office at 151A Sydney Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7158,46 +7175,46 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Gemic</t>
+          <t>Morris+Company</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://www.gemic.com</t>
+          <t>https://www.morrisand.company</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Michelin House, 81 Fulham Road</t>
+          <t>215 Mare Street</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>SW3 6RD</t>
+          <t>E8 3QE</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>our South Kensington pitch on Thomas More Walk</t>
+          <t>our Hackney pitch on Homerton High Street</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>contact@gemic.com</t>
+          <t>london@morrisand.company</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -7205,8 +7222,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N77" s="3" t="inlineStr"/>
-      <c r="O77" s="2" t="inlineStr"/>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
+          <t>In December 2025 the practice won unanimous planning consent for its retrofit of 120 Holborn near Holborn Circus.</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.morrisand.company/about</t>
+        </is>
+      </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7215,18 +7240,19 @@
       <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/south-kensington</t>
+          <t>https://www.fcurban.com/location/hackney</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Gemic team</t>
+          <t>Weekly football for the Morris+Company team</t>
         </is>
       </c>
       <c r="T77" s="3" t="inlineStr">
         <is>
-          <t>Hi Gemic team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office at Michelin House, 81 Fulham Road.
+          <t>Hi Morris+Company team,
+In December 2025 the practice won unanimous planning consent for its retrofit of 120 Holborn near Holborn Circus.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Hackney pitch on Homerton High Street, about a 15 minute walk from your office at 215 Mare Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7239,46 +7265,46 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Zouk Capital</t>
+          <t>Dark Matter Labs</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://www.zouk.com</t>
+          <t>https://darkmatterlabs.org</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>26 Ives Street</t>
+          <t>217 Mare Street</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>SW3 2ND</t>
+          <t>E8 3QE</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>our South Kensington pitch on Thomas More Walk</t>
+          <t>our Hackney pitch on Homerton High Street</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>info@zouk.com</t>
+          <t>info@darkmatterlabs.org</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -7286,16 +7312,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N78" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on your portfolio company enspired closing a EUR 40 million Series B round last October.</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>https://www.zouk.com/news</t>
-        </is>
-      </c>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7304,19 +7322,18 @@
       <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/south-kensington</t>
+          <t>https://www.fcurban.com/location/hackney</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Zouk Capital team</t>
+          <t>Weekly football for the Dark Matter Labs team</t>
         </is>
       </c>
       <c r="T78" s="3" t="inlineStr">
         <is>
-          <t>Hi Zouk Capital team,
-Congratulations on your portfolio company enspired closing a EUR 40 million Series B round last October.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office at 26 Ives Street.
+          <t>Hi Dark Matter Labs team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Hackney pitch on Homerton High Street, about a 15 minute walk from your office at 217 Mare Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7329,46 +7346,46 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Cadogan</t>
+          <t>LDN Apprenticeships</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://www.cadogan.co.uk</t>
+          <t>https://www.ldnapprenticeships.com</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Other professional services</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>10 Duke of York Square</t>
+          <t>South Lambeth Road</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>SW3 4LY</t>
+          <t>SW8 1UJ</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>our South Kensington pitch on Thomas More Walk</t>
+          <t>our Kennington pitch on Hackford Road</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>info@cadogan.co.uk</t>
+          <t>hello@ldnapprenticeships.com</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -7376,16 +7393,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N79" s="3" t="inlineStr">
-        <is>
-          <t>I saw the Chelsea Arts Festival you host returns for its second year this month, from 16 to 20 September.</t>
-        </is>
-      </c>
-      <c r="O79" s="2" t="inlineStr">
-        <is>
-          <t>https://www.cadogan.co.uk/chelsea-arts-festival-17th-20th-september-2026/</t>
-        </is>
-      </c>
+      <c r="N79" s="3" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
       <c r="P79" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7394,19 +7403,18 @@
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/south-kensington</t>
+          <t>https://www.fcurban.com/location/kennington</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Cadogan team</t>
+          <t>Weekly football for the LDN Apprenticeships team</t>
         </is>
       </c>
       <c r="T79" s="3" t="inlineStr">
         <is>
-          <t>Hi Cadogan team,
-I saw the Chelsea Arts Festival you host returns for its second year this month, from 16 to 20 September.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 9 minute walk from your office at 10 Duke of York Square.
+          <t>Hi LDN Apprenticeships team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Kennington pitch on Hackford Road, about a 10 minute walk from your office on South Lambeth Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7419,30 +7427,30 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Scott Tallon Walker</t>
+          <t>Gemic</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://www.stwarchitects.com</t>
+          <t>https://www.gemic.com</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Consultancy</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>10 Cromwell Place</t>
+          <t>Michelin House, 81 Fulham Road</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>SW7 2JN</t>
+          <t>SW3 6RD</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -7451,14 +7459,14 @@
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>london@stwarchitects.com</t>
+          <t>contact@gemic.com</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -7466,16 +7474,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N80" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on breaking ground at Richmond Village in Fairview this spring, marked by your official sod turning ceremony in April.</t>
-        </is>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>https://www.stwarchitects.com/</t>
-        </is>
-      </c>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7489,14 +7489,13 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Scott Tallon Walker team</t>
+          <t>Weekly football for the Gemic team</t>
         </is>
       </c>
       <c r="T80" s="3" t="inlineStr">
         <is>
-          <t>Hi Scott Tallon Walker team,
-Congratulations on breaking ground at Richmond Village in Fairview this spring, marked by your official sod turning ceremony in April.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 10 minute walk from your office at 10 Cromwell Place.
+          <t>Hi Gemic team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office at Michelin House, 81 Fulham Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7509,30 +7508,30 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Kefron</t>
+          <t>Zouk Capital</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://kefron.com</t>
+          <t>https://www.zouk.com</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>120</v>
+        <v>23</v>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>21 Ellis Street</t>
+          <t>26 Ives Street</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>SW1X 9AL</t>
+          <t>SW3 2ND</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -7541,14 +7540,14 @@
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>info@kefron.com</t>
+          <t>info@zouk.com</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -7556,8 +7555,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N81" s="3" t="inlineStr"/>
-      <c r="O81" s="2" t="inlineStr"/>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on your portfolio company enspired closing a EUR 40 million Series B round last October.</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zouk.com/news</t>
+        </is>
+      </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7571,13 +7578,14 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Kefron team</t>
+          <t>Weekly football for the Zouk Capital team</t>
         </is>
       </c>
       <c r="T81" s="3" t="inlineStr">
         <is>
-          <t>Hi Kefron team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 21 Ellis Street.
+          <t>Hi Zouk Capital team,
+Congratulations on your portfolio company enspired closing a EUR 40 million Series B round last October.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 2 minute walk from your office at 26 Ives Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7590,30 +7598,30 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>venturethree</t>
+          <t>Cadogan</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://venturethree.com</t>
+          <t>https://www.cadogan.co.uk</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Other professional services</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>11 Cavalry Square</t>
+          <t>10 Duke of York Square</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>SW3 4RB</t>
+          <t>SW3 4LY</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -7622,14 +7630,14 @@
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>contact@venturethree.com</t>
+          <t>info@cadogan.co.uk</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -7637,8 +7645,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N82" s="3" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr"/>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
+          <t>I saw the Chelsea Arts Festival you host returns for its second year this month, from 16 to 20 September.</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cadogan.co.uk/chelsea-arts-festival-17th-20th-september-2026/</t>
+        </is>
+      </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7652,13 +7668,14 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the venturethree team</t>
+          <t>Weekly football for the Cadogan team</t>
         </is>
       </c>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>Hi venturethree team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 11 Cavalry Square.
+          <t>Hi Cadogan team,
+I saw the Chelsea Arts Festival you host returns for its second year this month, from 16 to 20 September.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 9 minute walk from your office at 10 Duke of York Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7671,30 +7688,30 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Andurand Capital</t>
+          <t>Scott Tallon Walker</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://www.andurandcapital.com</t>
+          <t>https://www.stwarchitects.com</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>100 Brompton Road</t>
+          <t>10 Cromwell Place</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>SW3 1ER</t>
+          <t>SW7 2JN</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -7703,14 +7720,14 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>contact@andurandcapital.com</t>
+          <t>london@stwarchitects.com</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -7718,8 +7735,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N83" s="3" t="inlineStr"/>
-      <c r="O83" s="2" t="inlineStr"/>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on breaking ground at Richmond Village in Fairview this spring, marked by your official sod turning ceremony in April.</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.stwarchitects.com/</t>
+        </is>
+      </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7733,13 +7758,14 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Andurand Capital team</t>
+          <t>Weekly football for the Scott Tallon Walker team</t>
         </is>
       </c>
       <c r="T83" s="3" t="inlineStr">
         <is>
-          <t>Hi Andurand Capital team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 13 minute walk from your office at 100 Brompton Road.
+          <t>Hi Scott Tallon Walker team,
+Congratulations on breaking ground at Richmond Village in Fairview this spring, marked by your official sod turning ceremony in April.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 10 minute walk from your office at 10 Cromwell Place.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7752,12 +7778,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Trifork</t>
+          <t>Kefron</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://trifork.com</t>
+          <t>https://kefron.com</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
@@ -7770,28 +7796,28 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>14 Gowers Walk</t>
+          <t>21 Ellis Street</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>E1 8PY</t>
+          <t>SW1X 9AL</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>our Whitechapel pitch on Richard Street</t>
+          <t>our South Kensington pitch on Thomas More Walk</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>info@trifork.com</t>
+          <t>info@kefron.com</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -7799,16 +7825,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N84" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on your new SAP Customer Experience reseller agreement, announced this September.</t>
-        </is>
-      </c>
-      <c r="O84" s="2" t="inlineStr">
-        <is>
-          <t>https://trifork.com/</t>
-        </is>
-      </c>
+      <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
       <c r="P84" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7817,19 +7835,18 @@
       <c r="Q84" s="2" t="inlineStr"/>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/whitechapel</t>
+          <t>https://www.fcurban.com/location/south-kensington</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Trifork team</t>
+          <t>Weekly football for the Kefron team</t>
         </is>
       </c>
       <c r="T84" s="3" t="inlineStr">
         <is>
-          <t>Hi Trifork team,
-Congratulations on your new SAP Customer Experience reseller agreement, announced this September.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Whitechapel pitch on Richard Street, about a 9 minute walk from your office at 14 Gowers Walk.
+          <t>Hi Kefron team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 21 Ellis Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7842,12 +7859,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>G2 Speech</t>
+          <t>venturethree</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://www.g2speech.com</t>
+          <t>https://venturethree.com</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
@@ -7855,33 +7872,33 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>10 Whites Row</t>
+          <t>11 Cavalry Square</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>E1 7NF</t>
+          <t>SW3 4RB</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>the Attlee Centre on Thrawl Street</t>
+          <t>our South Kensington pitch on Thomas More Walk</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>info@g2speech.com</t>
+          <t>contact@venturethree.com</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -7889,16 +7906,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N85" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on G2 Speech's appointment to the G Cloud 15 Framework this September, a great milestone.</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.g2speech.com/blog/g2-speech-appointed-to-g-cloud-15-framework</t>
-        </is>
-      </c>
+      <c r="N85" s="3" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
       <c r="P85" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -7907,19 +7916,18 @@
       <c r="Q85" s="2" t="inlineStr"/>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+          <t>https://www.fcurban.com/location/south-kensington</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the G2 Speech team</t>
+          <t>Weekly football for the venturethree team</t>
         </is>
       </c>
       <c r="T85" s="3" t="inlineStr">
         <is>
-          <t>Hi G2 Speech team,
-Congratulations on G2 Speech's appointment to the G Cloud 15 Framework this September, a great milestone.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 3 minute walk from your office at 10 Whites Row.
+          <t>Hi venturethree team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about an 11 minute walk from your office at 11 Cavalry Square.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -7932,46 +7940,46 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Opply</t>
+          <t>Andurand Capital</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://opply.com</t>
+          <t>https://www.andurandcapital.com</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>42-46 Princelet Street</t>
+          <t>100 Brompton Road</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>E1 5LP</t>
+          <t>SW3 1ER</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>the Attlee Centre on Thrawl Street</t>
+          <t>our South Kensington pitch on Thomas More Walk</t>
         </is>
       </c>
       <c r="H86" s="2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>hello@opply.com</t>
+          <t>contact@andurandcapital.com</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -7989,18 +7997,18 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+          <t>https://www.fcurban.com/location/south-kensington</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Opply team</t>
+          <t>Weekly football for the Andurand Capital team</t>
         </is>
       </c>
       <c r="T86" s="3" t="inlineStr">
         <is>
-          <t>Hi Opply team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 4 minute walk from your office at 42-46 Princelet Street.
+          <t>Hi Andurand Capital team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our South Kensington pitch on Thomas More Walk, about a 13 minute walk from your office at 100 Brompton Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8013,16 +8021,16 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>CyberSmart</t>
+          <t>Trifork</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://cybersmart.co.uk</t>
+          <t>https://trifork.com</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
@@ -8031,28 +8039,28 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Hanbury Street</t>
+          <t>14 Gowers Walk</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>E1 5JL</t>
+          <t>E1 8PY</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>the Attlee Centre on Thrawl Street</t>
+          <t>our Whitechapel pitch on Richard Street</t>
         </is>
       </c>
       <c r="H87" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>hello@cybersmart.co.uk</t>
+          <t>info@trifork.com</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -8060,8 +8068,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="2" t="inlineStr"/>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on your new SAP Customer Experience reseller agreement, announced this September.</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>https://trifork.com/</t>
+        </is>
+      </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8070,18 +8086,19 @@
       <c r="Q87" s="2" t="inlineStr"/>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+          <t>https://www.fcurban.com/location/whitechapel</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the CyberSmart team</t>
+          <t>Weekly football for the Trifork team</t>
         </is>
       </c>
       <c r="T87" s="3" t="inlineStr">
         <is>
-          <t>Hi CyberSmart team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office on Hanbury Street.
+          <t>Hi Trifork team,
+Congratulations on your new SAP Customer Experience reseller agreement, announced this September.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at our Whitechapel pitch on Richard Street, about a 9 minute walk from your office at 14 Gowers Walk.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8094,30 +8111,30 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Hereworks</t>
+          <t>G2 Speech</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://www.hereworks.io</t>
+          <t>https://www.g2speech.com</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Engineering consultancy</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>61 Whitechapel High Street</t>
+          <t>10 Whites Row</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>E1 7PE</t>
+          <t>E1 7NF</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -8126,14 +8143,14 @@
         </is>
       </c>
       <c r="H88" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>info@hereworks.io</t>
+          <t>info@g2speech.com</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -8143,12 +8160,12 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on opening your new London office on Whitechapel High Street this summer.</t>
+          <t>Congratulations on G2 Speech's appointment to the G Cloud 15 Framework this September, a great milestone.</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>https://www.hereworks.io/tech-talk/hereworks-opens-new-uk-office-in-london</t>
+          <t>https://www.g2speech.com/blog/g2-speech-appointed-to-g-cloud-15-framework</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -8164,14 +8181,14 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Hereworks team</t>
+          <t>Weekly football for the G2 Speech team</t>
         </is>
       </c>
       <c r="T88" s="3" t="inlineStr">
         <is>
-          <t>Hi Hereworks team,
-Congratulations on opening your new London office on Whitechapel High Street this summer.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office at 61 Whitechapel High Street.
+          <t>Hi G2 Speech team,
+Congratulations on G2 Speech's appointment to the G Cloud 15 Framework this September, a great milestone.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 3 minute walk from your office at 10 Whites Row.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8184,28 +8201,30 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Big Bad Wolf</t>
+          <t>Opply</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://www.bb-wolf.com</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr"/>
+          <t>https://opply.com</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Agency</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>75 Whitechapel Road</t>
+          <t>42-46 Princelet Street</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>E1 1DU</t>
+          <t>E1 5LP</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -8214,14 +8233,14 @@
         </is>
       </c>
       <c r="H89" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>london@bb-wolf.com</t>
+          <t>hello@opply.com</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -8244,13 +8263,13 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Big Bad Wolf team</t>
+          <t>Weekly football for the Opply team</t>
         </is>
       </c>
       <c r="T89" s="3" t="inlineStr">
         <is>
-          <t>Hi Big Bad Wolf team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office at 75 Whitechapel Road.
+          <t>Hi Opply team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 4 minute walk from your office at 42-46 Princelet Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8263,30 +8282,30 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Gravita</t>
+          <t>CyberSmart</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://www.gravita.com</t>
+          <t>https://cybersmart.co.uk</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2 Leman Street</t>
+          <t>Hanbury Street</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>E1 8FA</t>
+          <t>E1 5JL</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -8295,14 +8314,14 @@
         </is>
       </c>
       <c r="H90" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>hello@gravita.com</t>
+          <t>hello@cybersmart.co.uk</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
@@ -8310,16 +8329,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N90" s="3" t="inlineStr">
-        <is>
-          <t>I saw Gravita welcomed the award winning charity accountants Godfrey Wilson this summer, taking your not for profit client base past 1,100 organisations.</t>
-        </is>
-      </c>
-      <c r="O90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gravita.com/insights/award-winning-charity-accountants-godfrey-wilson-join-gravita/</t>
-        </is>
-      </c>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
       <c r="P90" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8333,14 +8344,13 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Gravita team</t>
+          <t>Weekly football for the CyberSmart team</t>
         </is>
       </c>
       <c r="T90" s="3" t="inlineStr">
         <is>
-          <t>Hi Gravita team,
-I saw Gravita welcomed the award winning charity accountants Godfrey Wilson this summer, taking your not for profit client base past 1,100 organisations.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 6 minute walk from your office at 2 Leman Street.
+          <t>Hi CyberSmart team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office on Hanbury Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8353,28 +8363,30 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>JAC Recruitment UK</t>
+          <t>Hereworks</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://www.jac-recruitment.co.uk</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr"/>
+          <t>https://www.hereworks.io</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>20</v>
+      </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Engineering consultancy</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>2 Leman Street, Aldgate Tower</t>
+          <t>61 Whitechapel High Street</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>E1 8FA</t>
+          <t>E1 7PE</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -8383,14 +8395,14 @@
         </is>
       </c>
       <c r="H91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>london@jac-recruitment.co.uk</t>
+          <t>info@hereworks.io</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
@@ -8398,8 +8410,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N91" s="3" t="inlineStr"/>
-      <c r="O91" s="2" t="inlineStr"/>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on opening your new London office on Whitechapel High Street this summer.</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hereworks.io/tech-talk/hereworks-opens-new-uk-office-in-london</t>
+        </is>
+      </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8413,13 +8433,14 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the JAC Recruitment UK team</t>
+          <t>Weekly football for the Hereworks team</t>
         </is>
       </c>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>Hi JAC Recruitment UK team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 6 minute walk from your office at 2 Leman Street, Aldgate Tower.
+          <t>Hi Hereworks team,
+Congratulations on opening your new London office on Whitechapel High Street this summer.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office at 61 Whitechapel High Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8432,30 +8453,28 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Ziipline</t>
+          <t>Big Bad Wolf</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://www.ziipline.com</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n">
-        <v>55</v>
-      </c>
+          <t>https://www.bb-wolf.com</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Agency</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>222 Bishopsgate</t>
+          <t>75 Whitechapel Road</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>EC2M 4QD</t>
+          <t>E1 1DU</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -8464,22 +8483,14 @@
         </is>
       </c>
       <c r="H92" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Ali Rabey</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>People &amp; Culture Manager</t>
-        </is>
-      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>hello@ziipline.com</t>
+          <t>london@bb-wolf.com</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -8487,16 +8498,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N92" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on your new strategic partnership with SimCorp, announced in February this year.</t>
-        </is>
-      </c>
-      <c r="O92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.ziipline.com/insights/simcorp-and-ziipline-announce-strategic-partnership</t>
-        </is>
-      </c>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
       <c r="P92" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8510,14 +8513,13 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Ziipline team</t>
+          <t>Weekly football for the Big Bad Wolf team</t>
         </is>
       </c>
       <c r="T92" s="3" t="inlineStr">
         <is>
-          <t>Hi Ali,
-Congratulations on your new strategic partnership with SimCorp, announced in February this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 7 minute walk from your office at 222 Bishopsgate.
+          <t>Hi Big Bad Wolf team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 5 minute walk from your office at 75 Whitechapel Road.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8530,30 +8532,30 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Morgan Hunt</t>
+          <t>Gravita</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://www.morganhunt.com</t>
+          <t>https://www.gravita.com</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>21 Mansell Street</t>
+          <t>2 Leman Street</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>E1 8AA</t>
+          <t>E1 8FA</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -8562,14 +8564,14 @@
         </is>
       </c>
       <c r="H93" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>londonadmin@morganhunt.com</t>
+          <t>hello@gravita.com</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
@@ -8577,8 +8579,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N93" s="3" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
+          <t>I saw Gravita welcomed the award winning charity accountants Godfrey Wilson this summer, taking your not for profit client base past 1,100 organisations.</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gravita.com/insights/award-winning-charity-accountants-godfrey-wilson-join-gravita/</t>
+        </is>
+      </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8592,13 +8602,14 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Morgan Hunt team</t>
+          <t>Weekly football for the Gravita team</t>
         </is>
       </c>
       <c r="T93" s="3" t="inlineStr">
         <is>
-          <t>Hi Morgan Hunt team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 7 minute walk from your office at 21 Mansell Street.
+          <t>Hi Gravita team,
+I saw Gravita welcomed the award winning charity accountants Godfrey Wilson this summer, taking your not for profit client base past 1,100 organisations.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 6 minute walk from your office at 2 Leman Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8611,17 +8622,15 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>DVF Recruitment</t>
+          <t>JAC Recruitment UK</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://www.dvfrecruitment.com</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n">
-        <v>75</v>
-      </c>
+          <t>https://www.jac-recruitment.co.uk</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Recruitment</t>
@@ -8629,12 +8638,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>10-12 Alie Street</t>
+          <t>2 Leman Street, Aldgate Tower</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>E1 8DE</t>
+          <t>E1 8FA</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -8643,14 +8652,14 @@
         </is>
       </c>
       <c r="H94" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>dvf@dvfrecruitment.com</t>
+          <t>london@jac-recruitment.co.uk</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
@@ -8673,13 +8682,13 @@
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the DVF Recruitment team</t>
+          <t>Weekly football for the JAC Recruitment UK team</t>
         </is>
       </c>
       <c r="T94" s="3" t="inlineStr">
         <is>
-          <t>Hi DVF Recruitment team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 8 minute walk from your office at 10-12 Alie Street.
+          <t>Hi JAC Recruitment UK team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 6 minute walk from your office at 2 Leman Street, Aldgate Tower.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8692,30 +8701,30 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>FactEntry</t>
+          <t>Ziipline</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://www.factentry.com</t>
+          <t>https://www.ziipline.com</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>201</v>
+        <v>55</v>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>33 St Mary Axe</t>
+          <t>222 Bishopsgate</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>EC3A 8AA</t>
+          <t>EC2M 4QD</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -8724,22 +8733,22 @@
         </is>
       </c>
       <c r="H95" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Tony McLaren</t>
+          <t>Ali Rabey</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Managing Director</t>
+          <t>People &amp; Culture Manager</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>info@factentry.com</t>
+          <t>hello@ziipline.com</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -8747,8 +8756,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on your new strategic partnership with SimCorp, announced in February this year.</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ziipline.com/insights/simcorp-and-ziipline-announce-strategic-partnership</t>
+        </is>
+      </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8762,13 +8779,14 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the FactEntry team</t>
+          <t>Weekly football for the Ziipline team</t>
         </is>
       </c>
       <c r="T95" s="3" t="inlineStr">
         <is>
-          <t>Hi Tony,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 33 St Mary Axe.
+          <t>Hi Ali,
+Congratulations on your new strategic partnership with SimCorp, announced in February this year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 7 minute walk from your office at 222 Bishopsgate.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8781,30 +8799,30 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Ultumus</t>
+          <t>Morgan Hunt</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://www.ultumus.com</t>
+          <t>https://www.morganhunt.com</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>54</v>
+        <v>150</v>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>33 St Mary Axe</t>
+          <t>21 Mansell Street</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>EC3A 8AA</t>
+          <t>E1 8AA</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -8813,14 +8831,14 @@
         </is>
       </c>
       <c r="H96" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>info@ultumus.com</t>
+          <t>londonadmin@morganhunt.com</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -8843,13 +8861,13 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Ultumus team</t>
+          <t>Weekly football for the Morgan Hunt team</t>
         </is>
       </c>
       <c r="T96" s="3" t="inlineStr">
         <is>
-          <t>Hi Ultumus team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 33 St Mary Axe.
+          <t>Hi Morgan Hunt team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 7 minute walk from your office at 21 Mansell Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8862,30 +8880,30 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Northell</t>
+          <t>DVF Recruitment</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://northell.com</t>
+          <t>https://www.dvfrecruitment.com</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Heron Tower, 110 Bishopsgate</t>
+          <t>10-12 Alie Street</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>EC2N 4AY</t>
+          <t>E1 8DE</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -8894,14 +8912,14 @@
         </is>
       </c>
       <c r="H97" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>info@northell.com</t>
+          <t>dvf@dvfrecruitment.com</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -8909,16 +8927,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N97" s="3" t="inlineStr">
-        <is>
-          <t>Congratulations on your December 2025 partnership with Clearcast, bringing Northell's explainable AI to UK television ad clearance.</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
-        <is>
-          <t>https://northell.com/insights/clearcast-and-northell-partner-to-bring-explainable-ai-to-uk-ad-clearance/</t>
-        </is>
-      </c>
+      <c r="N97" s="3" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
       <c r="P97" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -8932,14 +8942,13 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Northell team</t>
+          <t>Weekly football for the DVF Recruitment team</t>
         </is>
       </c>
       <c r="T97" s="3" t="inlineStr">
         <is>
-          <t>Hi Northell team,
-Congratulations on your December 2025 partnership with Clearcast, bringing Northell's explainable AI to UK television ad clearance.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at Heron Tower, 110 Bishopsgate.
+          <t>Hi DVF Recruitment team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 8 minute walk from your office at 10-12 Alie Street.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -8952,30 +8961,30 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>CYPFER</t>
+          <t>FactEntry</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://cypfer.com</t>
+          <t>https://www.factentry.com</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>30 St. Mary Axe</t>
+          <t>33 St Mary Axe</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>EC3A 8EP</t>
+          <t>EC3A 8AA</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -8987,11 +8996,19 @@
         <v>10</v>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-      <c r="K98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Tony McLaren</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>info@cypfer.com</t>
+          <t>info@factentry.com</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -9014,13 +9031,13 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the CYPFER team</t>
+          <t>Weekly football for the FactEntry team</t>
         </is>
       </c>
       <c r="T98" s="3" t="inlineStr">
         <is>
-          <t>Hi CYPFER team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 30 St. Mary Axe.
+          <t>Hi Tony,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 33 St Mary Axe.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9033,28 +9050,30 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Celon</t>
+          <t>Ultumus</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://www.celon.co.uk</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr"/>
+          <t>https://www.ultumus.com</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>54</v>
+      </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>100 Bishopsgate</t>
+          <t>33 St Mary Axe</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>EC2N 4AG</t>
+          <t>EC3A 8AA</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -9070,7 +9089,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>hello@celon.co.uk</t>
+          <t>info@ultumus.com</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -9093,13 +9112,13 @@
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Celon team</t>
+          <t>Weekly football for the Ultumus team</t>
         </is>
       </c>
       <c r="T99" s="3" t="inlineStr">
         <is>
-          <t>Hi Celon team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 100 Bishopsgate.
+          <t>Hi Ultumus team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 33 St Mary Axe.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9112,12 +9131,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>C-Quence</t>
+          <t>Northell</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-quence.co.uk</t>
+          <t>https://northell.com</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
@@ -9125,17 +9144,17 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>63 St Mary Axe</t>
+          <t>Heron Tower, 110 Bishopsgate</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>EC3A 8AA</t>
+          <t>EC2N 4AY</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -9147,19 +9166,11 @@
         <v>10</v>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Jacqueline McNamee</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Founder &amp; CEO</t>
-        </is>
-      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>enquiries@c-quence.co.uk</t>
+          <t>info@northell.com</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
@@ -9169,12 +9180,12 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on welcoming two experienced P&amp;C underwriters, Jenny Attewell and Gemma Walters, to the team this year.</t>
+          <t>Congratulations on your December 2025 partnership with Clearcast, bringing Northell's explainable AI to UK television ad clearance.</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>https://www.c-quence.co.uk/blog/c-quence-expands-pc-underwriting-team-with-two-industry-experts</t>
+          <t>https://northell.com/insights/clearcast-and-northell-partner-to-bring-explainable-ai-to-uk-ad-clearance/</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -9190,14 +9201,14 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the C-Quence team</t>
+          <t>Weekly football for the Northell team</t>
         </is>
       </c>
       <c r="T100" s="3" t="inlineStr">
         <is>
-          <t>Hi Jacqueline,
-Congratulations on welcoming two experienced P&amp;C underwriters, Jenny Attewell and Gemma Walters, to the team this year.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 63 St Mary Axe.
+          <t>Hi Northell team,
+Congratulations on your December 2025 partnership with Clearcast, bringing Northell's explainable AI to UK television ad clearance.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at Heron Tower, 110 Bishopsgate.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9210,30 +9221,30 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Two Three Bird</t>
+          <t>CYPFER</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://www.twothreebird.com</t>
+          <t>https://cypfer.com</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>5 St Helen's Place</t>
+          <t>30 St. Mary Axe</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>EC3A 6AB</t>
+          <t>EC3A 8EP</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -9242,14 +9253,14 @@
         </is>
       </c>
       <c r="H101" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>hello@twothreebird.com</t>
+          <t>info@cypfer.com</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
@@ -9257,16 +9268,8 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N101" s="3" t="inlineStr">
-        <is>
-          <t>I saw your Sundays brand launched new electric bike insurance cover for UK delivery riders this January.</t>
-        </is>
-      </c>
-      <c r="O101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.twothreebird.com/newsroom</t>
-        </is>
-      </c>
+      <c r="N101" s="3" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -9280,14 +9283,13 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Two Three Bird team</t>
+          <t>Weekly football for the CYPFER team</t>
         </is>
       </c>
       <c r="T101" s="3" t="inlineStr">
         <is>
-          <t>Hi Two Three Bird team,
-I saw your Sundays brand launched new electric bike insurance cover for UK delivery riders this January.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 11 minute walk from your office at 5 St Helen's Place.
+          <t>Hi CYPFER team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 30 St. Mary Axe.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9300,28 +9302,28 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>CPP Group</t>
+          <t>Celon</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://uk.cppgroup.com</t>
+          <t>https://www.celon.co.uk</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>51 Lime Street</t>
+          <t>100 Bishopsgate</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>EC3M 7DQ</t>
+          <t>EC2N 4AG</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -9330,14 +9332,14 @@
         </is>
       </c>
       <c r="H102" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>hello@cppgroup.com</t>
+          <t>hello@celon.co.uk</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -9360,13 +9362,13 @@
       </c>
       <c r="S102" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the CPP Group team</t>
+          <t>Weekly football for the Celon team</t>
         </is>
       </c>
       <c r="T102" s="3" t="inlineStr">
         <is>
-          <t>Hi CPP Group team,
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 14 minute walk from your office at 51 Lime Street.
+          <t>Hi Celon team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 100 Bishopsgate.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9379,30 +9381,30 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Atheria Law</t>
+          <t>C-Quence</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://www.atherialaw.com</t>
+          <t>https://www.c-quence.co.uk</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>51 Lime Street</t>
+          <t>63 St Mary Axe</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>EC3M 7DQ</t>
+          <t>EC3A 8AA</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -9411,22 +9413,22 @@
         </is>
       </c>
       <c r="H103" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Our Team</t>
+          <t>Jacqueline McNamee</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Home Who We Are Why We Are Different Our Team Community Leadership Join Us What We Do Where We Are Our Insights News + Events Get In Touch</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>mary.weaver@atherialaw.com</t>
+          <t>enquiries@c-quence.co.uk</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -9436,12 +9438,12 @@
       </c>
       <c r="N103" s="3" t="inlineStr">
         <is>
-          <t>Congratulations on six of your lawyers being named to the 2027 Best Lawyers lists this August.</t>
+          <t>Congratulations on welcoming two experienced P&amp;C underwriters, Jenny Attewell and Gemma Walters, to the team this year.</t>
         </is>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>https://www.atherialaw.com/news-and-events</t>
+          <t>https://www.c-quence.co.uk/blog/c-quence-expands-pc-underwriting-team-with-two-industry-experts</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -9457,14 +9459,14 @@
       </c>
       <c r="S103" s="2" t="inlineStr">
         <is>
-          <t>Weekly football for the Atheria Law team</t>
+          <t>Weekly football for the C-Quence team</t>
         </is>
       </c>
       <c r="T103" s="3" t="inlineStr">
         <is>
-          <t>Hi Mary,
-Congratulations on six of your lawyers being named to the 2027 Best Lawyers lists this August.
-I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 14 minute walk from your office at 51 Lime Street.
+          <t>Hi Jacqueline,
+Congratulations on welcoming two experienced P&amp;C underwriters, Jenny Attewell and Gemma Walters, to the team this year.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 10 minute walk from your office at 63 St Mary Axe.
 We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
 Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
 Best,
@@ -9477,30 +9479,30 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Meaden &amp; Moore</t>
+          <t>Two Three Bird</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://www.meadenmoore.com</t>
+          <t>https://www.twothreebird.com</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>250</v>
+        <v>70</v>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Consultancy</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>1 Leadenhall Street</t>
+          <t>5 St Helen's Place</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>EC3V 1AB</t>
+          <t>EC3A 6AB</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -9509,14 +9511,14 @@
         </is>
       </c>
       <c r="H104" s="2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>info@meadenmoore.com</t>
+          <t>hello@twothreebird.com</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -9524,8 +9526,16 @@
           <t>generic</t>
         </is>
       </c>
-      <c r="N104" s="3" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
+          <t>I saw your Sundays brand launched new electric bike insurance cover for UK delivery riders this January.</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.twothreebird.com/newsroom</t>
+        </is>
+      </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
           <t>pass</t>
@@ -9539,10 +9549,269 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
+          <t>Weekly football for the Two Three Bird team</t>
+        </is>
+      </c>
+      <c r="T104" s="3" t="inlineStr">
+        <is>
+          <t>Hi Two Three Bird team,
+I saw your Sundays brand launched new electric bike insurance cover for UK delivery riders this January.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about an 11 minute walk from your office at 5 St Helen's Place.
+We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+Best,
+Brian
+FC Urban
+Reply with "no thanks" and I won't contact you again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>CPP Group</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>https://uk.cppgroup.com</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>51 Lime Street</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>EC3M 7DQ</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>the Attlee Centre on Thrawl Street</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>hello@cppgroup.com</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+        </is>
+      </c>
+      <c r="S105" s="2" t="inlineStr">
+        <is>
+          <t>Weekly football for the CPP Group team</t>
+        </is>
+      </c>
+      <c r="T105" s="3" t="inlineStr">
+        <is>
+          <t>Hi CPP Group team,
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 14 minute walk from your office at 51 Lime Street.
+We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+Best,
+Brian
+FC Urban
+Reply with "no thanks" and I won't contact you again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Atheria Law</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atherialaw.com</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>51 Lime Street</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>EC3M 7DQ</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>the Attlee Centre on Thrawl Street</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Our Team</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Home Who We Are Why We Are Different Our Team Community Leadership Join Us What We Do Where We Are Our Insights News + Events Get In Touch</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>mary.weaver@atherialaw.com</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
+          <t>Congratulations on six of your lawyers being named to the 2027 Best Lawyers lists this August.</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.atherialaw.com/news-and-events</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="inlineStr">
+        <is>
+          <t>Weekly football for the Atheria Law team</t>
+        </is>
+      </c>
+      <c r="T106" s="3" t="inlineStr">
+        <is>
+          <t>Hi Mary,
+Congratulations on six of your lawyers being named to the 2027 Best Lawyers lists this August.
+I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 14 minute walk from your office at 51 Lime Street.
+We'd love to help start a regular after work game for the team. We handle the pitch, the organisation and the payments, and if a few people can't make it we fill the spare places with our own players.
+Would there be any interest? If it's not for you, would you mind forwarding this to whoever looks after staff socials or wellbeing?
+Best,
+Brian
+FC Urban
+Reply with "no thanks" and I won't contact you again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Meaden &amp; Moore</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.meadenmoore.com</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Consultancy</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>1 Leadenhall Street</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>EC3V 1AB</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>the Attlee Centre on Thrawl Street</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>info@meadenmoore.com</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>generic</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.fcurban.com/location/liverpool-st-attlee-centre</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="inlineStr">
+        <is>
           <t>Weekly football for the Meaden &amp; Moore team</t>
         </is>
       </c>
-      <c r="T104" s="3" t="inlineStr">
+      <c r="T107" s="3" t="inlineStr">
         <is>
           <t>Hi Meaden &amp; Moore team,
 I'm Brian from FC Urban. We organise social football games across London, and we already run games at the Attlee Centre on Thrawl Street, about a 15 minute walk from your office at 1 Leadenhall Street.
@@ -9556,7 +9825,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T104"/>
+  <autoFilter ref="A1:T107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9583,7 +9852,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>103 companies, 31 near the three venues with confirmed slots (Borough Academy, St John's Wood, Poplar).</t>
+          <t>106 companies, 31 near the three venues with confirmed slots (Borough Academy, St John's Wood, Poplar).</t>
         </is>
       </c>
     </row>
